--- a/OUTPUT/direct_Q4UZF6_Xanthomonas_campestris_pv__campestris_str__ATCC_33913.xlsx
+++ b/OUTPUT/direct_Q4UZF6_Xanthomonas_campestris_pv__campestris_str__ATCC_33913.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.0182</v>
+        <v>0.01839264294282287</v>
       </c>
     </row>
   </sheetData>
